--- a/code/data/combined/cmb+dmul-lcdm-fixed.xlsx
+++ b/code/data/combined/cmb+dmul-lcdm-fixed.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -467,22 +467,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>39213914.00023862</v>
+        <v>44425444.09732961</v>
       </c>
       <c r="C2" t="n">
-        <v>-134286934.53813</v>
+        <v>-148685611.4239248</v>
       </c>
       <c r="D2" t="n">
-        <v>40645477.10334572</v>
+        <v>46689835.99113762</v>
       </c>
       <c r="E2" t="n">
-        <v>-410392.9037288567</v>
+        <v>-468237.0929703544</v>
       </c>
       <c r="F2" t="n">
-        <v>-1418702.450839485</v>
+        <v>-1421460.028066132</v>
       </c>
       <c r="G2" t="n">
-        <v>882064.6769764608</v>
+        <v>1050448.29779737</v>
       </c>
     </row>
     <row r="3">
@@ -492,22 +492,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-134286934.5381458</v>
+        <v>-148685611.4239354</v>
       </c>
       <c r="C3" t="n">
-        <v>887991069.1099135</v>
+        <v>895782919.2515694</v>
       </c>
       <c r="D3" t="n">
-        <v>-89476835.98496066</v>
+        <v>-111911249.001918</v>
       </c>
       <c r="E3" t="n">
-        <v>15741702.57410003</v>
+        <v>16344774.50350216</v>
       </c>
       <c r="F3" t="n">
-        <v>6695175.623846637</v>
+        <v>6648185.514448688</v>
       </c>
       <c r="G3" t="n">
-        <v>-3840600.547943572</v>
+        <v>-4444658.216509305</v>
       </c>
     </row>
     <row r="4">
@@ -517,22 +517,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40645477.10334438</v>
+        <v>46689835.9911363</v>
       </c>
       <c r="C4" t="n">
-        <v>-89476835.98494028</v>
+        <v>-111911249.0019033</v>
       </c>
       <c r="D4" t="n">
-        <v>49444924.03022194</v>
+        <v>55547151.11562501</v>
       </c>
       <c r="E4" t="n">
-        <v>942916.414389918</v>
+        <v>855710.4823316531</v>
       </c>
       <c r="F4" t="n">
-        <v>-1134934.082252183</v>
+        <v>-1159056.221530363</v>
       </c>
       <c r="G4" t="n">
-        <v>966618.6949262858</v>
+        <v>1147987.178654836</v>
       </c>
     </row>
     <row r="5">
@@ -542,22 +542,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-410392.9037294291</v>
+        <v>-468237.0929706817</v>
       </c>
       <c r="C5" t="n">
-        <v>15741702.57410211</v>
+        <v>16344774.50350348</v>
       </c>
       <c r="D5" t="n">
-        <v>942916.4143893599</v>
+        <v>855710.482331361</v>
       </c>
       <c r="E5" t="n">
-        <v>982978.4599449588</v>
+        <v>1070203.21464653</v>
       </c>
       <c r="F5" t="n">
-        <v>24342.1868453915</v>
+        <v>43220.67306817691</v>
       </c>
       <c r="G5" t="n">
-        <v>-74077.02687352253</v>
+        <v>-81632.91825365889</v>
       </c>
     </row>
     <row r="6">
@@ -567,22 +567,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1418702.450839421</v>
+        <v>-1421460.028066632</v>
       </c>
       <c r="C6" t="n">
-        <v>6695175.623845359</v>
+        <v>6648185.514449175</v>
       </c>
       <c r="D6" t="n">
-        <v>-1134934.082252169</v>
+        <v>-1159056.221531047</v>
       </c>
       <c r="E6" t="n">
-        <v>24342.18684534569</v>
+        <v>43220.67306813506</v>
       </c>
       <c r="F6" t="n">
-        <v>747842.710249897</v>
+        <v>748820.2786747231</v>
       </c>
       <c r="G6" t="n">
-        <v>107300.5175004464</v>
+        <v>106083.3443256252</v>
       </c>
     </row>
     <row r="7">
@@ -592,22 +592,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>882064.6769765791</v>
+        <v>1050448.297797292</v>
       </c>
       <c r="C7" t="n">
-        <v>-3840600.547943784</v>
+        <v>-4444658.216509098</v>
       </c>
       <c r="D7" t="n">
-        <v>966618.6949264259</v>
+        <v>1147987.178654745</v>
       </c>
       <c r="E7" t="n">
-        <v>-74077.02687351714</v>
+        <v>-81632.91825366075</v>
       </c>
       <c r="F7" t="n">
-        <v>107300.517500436</v>
+        <v>106083.3443256356</v>
       </c>
       <c r="G7" t="n">
-        <v>66677.42738965605</v>
+        <v>72577.55397030419</v>
       </c>
     </row>
   </sheetData>

--- a/code/data/combined/cmb+dmul-lcdm-fixed.xlsx
+++ b/code/data/combined/cmb+dmul-lcdm-fixed.xlsx
@@ -467,22 +467,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>44425444.09732961</v>
+        <v>43575294.85646555</v>
       </c>
       <c r="C2" t="n">
-        <v>-148685611.4239248</v>
+        <v>-145846347.9144342</v>
       </c>
       <c r="D2" t="n">
-        <v>46689835.99113762</v>
+        <v>45770888.47553694</v>
       </c>
       <c r="E2" t="n">
-        <v>-468237.0929703544</v>
+        <v>-460982.2861886937</v>
       </c>
       <c r="F2" t="n">
-        <v>-1421460.028066132</v>
+        <v>-1413843.634407594</v>
       </c>
       <c r="G2" t="n">
-        <v>1050448.29779737</v>
+        <v>1023557.718754368</v>
       </c>
     </row>
     <row r="3">
@@ -492,22 +492,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-148685611.4239354</v>
+        <v>-145846347.9143901</v>
       </c>
       <c r="C3" t="n">
-        <v>895782919.2515694</v>
+        <v>876933849.1275738</v>
       </c>
       <c r="D3" t="n">
-        <v>-111911249.001918</v>
+        <v>-110082289.0534475</v>
       </c>
       <c r="E3" t="n">
-        <v>16344774.50350216</v>
+        <v>16113321.63830155</v>
       </c>
       <c r="F3" t="n">
-        <v>6648185.514448688</v>
+        <v>6575874.493003272</v>
       </c>
       <c r="G3" t="n">
-        <v>-4444658.216509305</v>
+        <v>-4351201.155642869</v>
       </c>
     </row>
     <row r="4">
@@ -517,22 +517,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>46689835.9911363</v>
+        <v>45770888.47554123</v>
       </c>
       <c r="C4" t="n">
-        <v>-111911249.0019033</v>
+        <v>-110082289.0535078</v>
       </c>
       <c r="D4" t="n">
-        <v>55547151.11562501</v>
+        <v>54387207.00180516</v>
       </c>
       <c r="E4" t="n">
-        <v>855710.4823316531</v>
+        <v>837194.9054087675</v>
       </c>
       <c r="F4" t="n">
-        <v>-1159056.221530363</v>
+        <v>-1155120.540673289</v>
       </c>
       <c r="G4" t="n">
-        <v>1147987.178654836</v>
+        <v>1119448.476683106</v>
       </c>
     </row>
     <row r="5">
@@ -542,22 +542,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-468237.0929706817</v>
+        <v>-460982.2861868582</v>
       </c>
       <c r="C5" t="n">
-        <v>16344774.50350348</v>
+        <v>16113321.63829572</v>
       </c>
       <c r="D5" t="n">
-        <v>855710.482331361</v>
+        <v>837194.9054107027</v>
       </c>
       <c r="E5" t="n">
-        <v>1070203.21464653</v>
+        <v>1062321.036112347</v>
       </c>
       <c r="F5" t="n">
-        <v>43220.67306817691</v>
+        <v>43141.09559424543</v>
       </c>
       <c r="G5" t="n">
-        <v>-81632.91825365889</v>
+        <v>-81084.23474120823</v>
       </c>
     </row>
     <row r="6">
@@ -567,22 +567,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-1421460.028066632</v>
+        <v>-1413843.634407757</v>
       </c>
       <c r="C6" t="n">
-        <v>6648185.514449175</v>
+        <v>6575874.493005686</v>
       </c>
       <c r="D6" t="n">
-        <v>-1159056.221531047</v>
+        <v>-1155120.540673297</v>
       </c>
       <c r="E6" t="n">
-        <v>43220.67306813506</v>
+        <v>43141.09559432704</v>
       </c>
       <c r="F6" t="n">
-        <v>748820.2786747231</v>
+        <v>744664.3838415849</v>
       </c>
       <c r="G6" t="n">
-        <v>106083.3443256252</v>
+        <v>105952.213950048</v>
       </c>
     </row>
     <row r="7">
@@ -592,22 +592,22 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1050448.297797292</v>
+        <v>1023557.718754101</v>
       </c>
       <c r="C7" t="n">
-        <v>-4444658.216509098</v>
+        <v>-4351201.155642851</v>
       </c>
       <c r="D7" t="n">
-        <v>1147987.178654745</v>
+        <v>1119448.476682739</v>
       </c>
       <c r="E7" t="n">
-        <v>-81632.91825366075</v>
+        <v>-81084.23474124144</v>
       </c>
       <c r="F7" t="n">
-        <v>106083.3443256356</v>
+        <v>105952.2139500635</v>
       </c>
       <c r="G7" t="n">
-        <v>72577.55397030419</v>
+        <v>71670.12459125184</v>
       </c>
     </row>
   </sheetData>
